--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487069_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487069_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.2834</v>
+        <v>7.7296</v>
       </c>
       <c r="E2" t="n">
-        <v>6.5516</v>
+        <v>6.971</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7319</v>
+        <v>0.7586000000000001</v>
       </c>
       <c r="G2" t="n">
         <v>6.5326</v>
@@ -610,13 +610,13 @@
         <v>2.8951</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.7933</v>
+        <v>-1.3471</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1765</v>
+        <v>-0.7571</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6167</v>
+        <v>-0.59</v>
       </c>
       <c r="V2" t="n">
         <v>0.614</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.4856</v>
+        <v>1.9091</v>
       </c>
       <c r="E3" t="n">
-        <v>2.2392</v>
+        <v>0.5557</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2464</v>
+        <v>1.3534</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0198</v>
@@ -688,13 +688,13 @@
         <v>2.1231</v>
       </c>
       <c r="S3" t="n">
-        <v>1.4053</v>
+        <v>-0.1712</v>
       </c>
       <c r="T3" t="n">
-        <v>1.8508</v>
+        <v>0.1673</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4455</v>
+        <v>-0.3385</v>
       </c>
       <c r="V3" t="n">
         <v>0.9421</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0562</v>
+        <v>1.1901</v>
       </c>
       <c r="E4" t="n">
         <v>-0.0247</v>
       </c>
       <c r="F4" t="n">
-        <v>1.0809</v>
+        <v>1.2147</v>
       </c>
       <c r="G4" t="n">
         <v>2.3003</v>
@@ -766,13 +766,13 @@
         <v>1.7371</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.7073</v>
+        <v>-1.5735</v>
       </c>
       <c r="T4" t="n">
         <v>-0.6411</v>
       </c>
       <c r="U4" t="n">
-        <v>-1.0662</v>
+        <v>-0.9324</v>
       </c>
       <c r="V4" t="n">
         <v>0.6562</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.3698</v>
+        <v>-1.3301</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0407</v>
+        <v>-0.8404</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.3291</v>
+        <v>-0.4897</v>
       </c>
       <c r="G5" t="n">
         <v>-1.7531</v>
@@ -844,13 +844,13 @@
         <v>0.772</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3887</v>
+        <v>-0.349</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4759</v>
+        <v>-0.2756</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0872</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.8295</v>
+        <v>-1.6956</v>
       </c>
       <c r="E6" t="n">
         <v>-0.9157999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9136</v>
+        <v>-0.7798</v>
       </c>
       <c r="G6" t="n">
         <v>-2.2294</v>
@@ -922,13 +922,13 @@
         <v>0.772</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3721</v>
+        <v>-0.2383</v>
       </c>
       <c r="T6" t="n">
         <v>0.0727</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4449</v>
+        <v>-0.311</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.0022</v>
+        <v>-1.7434</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2015</v>
+        <v>1.6209</v>
       </c>
       <c r="F7" t="n">
-        <v>-3.2037</v>
+        <v>-3.3643</v>
       </c>
       <c r="G7" t="n">
         <v>-0.6788</v>
@@ -1000,13 +1000,13 @@
         <v>2.1231</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9677</v>
+        <v>-0.7089</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0113</v>
+        <v>-0.5919</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0436</v>
+        <v>-0.117</v>
       </c>
       <c r="V7" t="n">
         <v>-1.5138</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0869</v>
+        <v>-2.4151</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.407</v>
+        <v>-2.3069</v>
       </c>
       <c r="F8" t="n">
-        <v>0.3201</v>
+        <v>-0.1082</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5456</v>
@@ -1078,13 +1078,13 @@
         <v>1.158</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.5063</v>
+        <v>-0.8345</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.5221</v>
+        <v>-0.422</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0158</v>
+        <v>-0.4125</v>
       </c>
       <c r="V8" t="n">
         <v>-1.228</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1795</v>
+        <v>-2.6253</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.2979</v>
+        <v>-2.7972</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1184</v>
+        <v>0.172</v>
       </c>
       <c r="G9" t="n">
         <v>-2.2136</v>
@@ -1156,13 +1156,13 @@
         <v>0.965</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9888</v>
+        <v>-0.4346</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.6544</v>
+        <v>-0.1537</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3345</v>
+        <v>-0.2809</v>
       </c>
       <c r="V9" t="n">
         <v>-0.9421</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. SAVITSKI SAVITSKAIA</t>
+          <t>A. ARBIZU MAIZA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5001</v>
+        <v>-2.8849</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.9275</v>
+        <v>-1.6566</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.5726</v>
+        <v>-1.2283</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1294</v>
+        <v>-1.1262</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2341</v>
+        <v>1.5392</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8954</v>
+        <v>-2.6654</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.2355</v>
+        <v>0.08740000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.3671</v>
+        <v>1.3661</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6026</v>
+        <v>-1.2788</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.894</v>
+        <v>-1.2136</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6012</v>
+        <v>0.1731</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2928</v>
+        <v>-1.3866</v>
       </c>
       <c r="P10" t="n">
-        <v>0.386</v>
+        <v>1.5441</v>
       </c>
       <c r="Q10" t="n">
         <v>-0.965</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3511</v>
+        <v>2.5091</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8725000000000001</v>
+        <v>-1.5031</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0708</v>
+        <v>-0.7789</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1983</v>
+        <v>-0.7242</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8842</v>
+        <v>-1.7997</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6562</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.228</v>
+        <v>-1.7997</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. ARBIZU MAIZA</t>
+          <t>A. SAVITSKI SAVITSKAIA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.5056</v>
+        <v>-3.1878</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.8757</v>
+        <v>-2.5081</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6298</v>
+        <v>-0.6797</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.1262</v>
+        <v>-1.1294</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5392</v>
+        <v>-0.2341</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.6654</v>
+        <v>-0.8954</v>
       </c>
       <c r="J11" t="n">
-        <v>0.08740000000000001</v>
+        <v>-0.2355</v>
       </c>
       <c r="K11" t="n">
-        <v>1.3661</v>
+        <v>0.3671</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.2788</v>
+        <v>-0.6026</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2136</v>
+        <v>-0.894</v>
       </c>
       <c r="N11" t="n">
-        <v>0.1731</v>
+        <v>-0.6012</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.3866</v>
+        <v>-0.2928</v>
       </c>
       <c r="P11" t="n">
-        <v>1.5441</v>
+        <v>0.386</v>
       </c>
       <c r="Q11" t="n">
         <v>-0.965</v>
       </c>
       <c r="R11" t="n">
-        <v>2.5091</v>
+        <v>1.3511</v>
       </c>
       <c r="S11" t="n">
-        <v>-2.1237</v>
+        <v>-0.5602</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9981</v>
+        <v>-0.6514</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.1257</v>
+        <v>0.0912</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7997</v>
+        <v>-1.8842</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.6562</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.7997</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.6484</v>
+        <v>-5.053400000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.497000000000002</v>
+        <v>-1.902100000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.1511</v>
+        <v>-3.1513</v>
       </c>
       <c r="G12" t="n">
         <v>-0.8629999999999993</v>
@@ -1381,7 +1381,7 @@
         <v>-7.6653</v>
       </c>
       <c r="P12" t="n">
-        <v>8.6852</v>
+        <v>8.685199999999998</v>
       </c>
       <c r="Q12" t="n">
         <v>-7.7201</v>
@@ -1390,16 +1390,16 @@
         <v>16.4056</v>
       </c>
       <c r="S12" t="n">
-        <v>-8.315099999999999</v>
+        <v>-7.7204</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.6267</v>
+        <v>-4.0317</v>
       </c>
       <c r="U12" t="n">
-        <v>-3.688599999999999</v>
+        <v>-3.688699999999999</v>
       </c>
       <c r="V12" t="n">
-        <v>-5.1555</v>
+        <v>-5.155500000000001</v>
       </c>
       <c r="W12" t="n">
         <v>4.2135</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>7.3041</v>
+        <v>8.0457</v>
       </c>
       <c r="E13" t="n">
-        <v>7.3158</v>
+        <v>7.8165</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0117</v>
+        <v>0.2292</v>
       </c>
       <c r="G13" t="n">
         <v>7.4977</v>
@@ -1468,13 +1468,13 @@
         <v>1.3511</v>
       </c>
       <c r="S13" t="n">
-        <v>0.6207</v>
+        <v>1.3623</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1891</v>
+        <v>0.6898</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4316</v>
+        <v>0.6725</v>
       </c>
       <c r="V13" t="n">
         <v>-0.0422</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.6677</v>
+        <v>3.1962</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7262</v>
+        <v>1.8263</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9415</v>
+        <v>1.3698</v>
       </c>
       <c r="G14" t="n">
         <v>3.4966</v>
@@ -1546,13 +1546,13 @@
         <v>0.386</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2498</v>
+        <v>0.2786</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2842</v>
+        <v>-0.1841</v>
       </c>
       <c r="U14" t="n">
-        <v>0.0344</v>
+        <v>0.4627</v>
       </c>
       <c r="V14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>C. RIVERA MOTA</t>
+          <t>G. TSULAIA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5044</v>
+        <v>3.1916</v>
       </c>
       <c r="E15" t="n">
-        <v>-1.1112</v>
+        <v>1.982</v>
       </c>
       <c r="F15" t="n">
-        <v>3.6157</v>
+        <v>1.2096</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.9676</v>
+        <v>1.4555</v>
       </c>
       <c r="H15" t="n">
-        <v>-3.3742</v>
+        <v>-1.9632</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4066</v>
+        <v>3.4187</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.954</v>
+        <v>1.8084</v>
       </c>
       <c r="K15" t="n">
-        <v>-2.9397</v>
+        <v>-1.3818</v>
       </c>
       <c r="L15" t="n">
-        <v>1.9857</v>
+        <v>3.1903</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.0136</v>
+        <v>-0.3529</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.4345</v>
+        <v>-0.5814</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.5790999999999999</v>
+        <v>0.2285</v>
       </c>
       <c r="P15" t="n">
-        <v>-3.0881</v>
+        <v>-2.5091</v>
       </c>
       <c r="Q15" t="n">
-        <v>-4.0532</v>
+        <v>-3.8602</v>
       </c>
       <c r="R15" t="n">
-        <v>0.965</v>
+        <v>1.3511</v>
       </c>
       <c r="S15" t="n">
-        <v>3.5059</v>
+        <v>0.9317</v>
       </c>
       <c r="T15" t="n">
-        <v>1.1541</v>
+        <v>0.7202</v>
       </c>
       <c r="U15" t="n">
-        <v>2.3517</v>
+        <v>0.2115</v>
       </c>
       <c r="V15" t="n">
-        <v>4.0543</v>
+        <v>3.3135</v>
       </c>
       <c r="W15" t="n">
-        <v>2.7418</v>
+        <v>3.3135</v>
       </c>
       <c r="X15" t="n">
-        <v>1.3125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>G. TSULAIA</t>
+          <t>C. RIVERA MOTA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.5408</v>
+        <v>1.4009</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0807</v>
+        <v>-1.4117</v>
       </c>
       <c r="F16" t="n">
-        <v>0.46</v>
+        <v>2.8126</v>
       </c>
       <c r="G16" t="n">
-        <v>1.4555</v>
+        <v>-1.9676</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9632</v>
+        <v>-3.3742</v>
       </c>
       <c r="I16" t="n">
-        <v>3.4187</v>
+        <v>1.4066</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8084</v>
+        <v>-0.954</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.3818</v>
+        <v>-2.9397</v>
       </c>
       <c r="L16" t="n">
-        <v>3.1903</v>
+        <v>1.9857</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.3529</v>
+        <v>-1.0136</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.5814</v>
+        <v>-0.4345</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2285</v>
+        <v>-0.5790999999999999</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.5091</v>
+        <v>-3.0881</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.8602</v>
+        <v>-4.0532</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3511</v>
+        <v>0.965</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7191</v>
+        <v>2.4023</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1811</v>
+        <v>0.8537</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5381</v>
+        <v>1.5486</v>
       </c>
       <c r="V16" t="n">
-        <v>3.3135</v>
+        <v>4.0543</v>
       </c>
       <c r="W16" t="n">
-        <v>3.3135</v>
+        <v>2.7418</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>1.3125</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.5592</v>
+        <v>-0.0813</v>
       </c>
       <c r="E17" t="n">
-        <v>0.493</v>
+        <v>-0.3082</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0663</v>
+        <v>0.2269</v>
       </c>
       <c r="G17" t="n">
         <v>-0.2446</v>
@@ -1780,13 +1780,13 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8038</v>
+        <v>0.1633</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0378</v>
+        <v>0.2366</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.234</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.2756</v>
+        <v>-0.2221</v>
       </c>
       <c r="E18" t="n">
         <v>0.0426</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3182</v>
+        <v>-0.2647</v>
       </c>
       <c r="G18" t="n">
         <v>-0.1183</v>
@@ -1858,13 +1858,13 @@
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.1573</v>
+        <v>-0.1038</v>
       </c>
       <c r="T18" t="n">
         <v>-0.0595</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0978</v>
+        <v>-0.0443</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. CAMPBELL</t>
+          <t>D. IBARLUCEA LAVIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.0071</v>
+        <v>-2.1514</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8699</v>
+        <v>-2.4534</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8629</v>
+        <v>0.302</v>
       </c>
       <c r="G19" t="n">
-        <v>-4.4609</v>
+        <v>-2.2814</v>
       </c>
       <c r="H19" t="n">
-        <v>-3.9403</v>
+        <v>-0.9169</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5205</v>
+        <v>-1.3645</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.9984</v>
+        <v>-1.7746</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6564</v>
+        <v>-0.5693</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.342</v>
+        <v>-1.2052</v>
       </c>
       <c r="M19" t="n">
-        <v>-2.4625</v>
+        <v>-0.5068</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.284</v>
+        <v>-0.3476</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.1785</v>
+        <v>-0.1592</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7371</v>
+        <v>0.386</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.0881</v>
+        <v>-1.158</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3511</v>
+        <v>1.5441</v>
       </c>
       <c r="S19" t="n">
-        <v>3.6771</v>
+        <v>0.972</v>
       </c>
       <c r="T19" t="n">
-        <v>1.7028</v>
+        <v>0.4793</v>
       </c>
       <c r="U19" t="n">
-        <v>1.9743</v>
+        <v>0.4927</v>
       </c>
       <c r="V19" t="n">
-        <v>1.5138</v>
+        <v>-1.228</v>
       </c>
       <c r="W19" t="n">
-        <v>1.5138</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-1.228</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. IBARLUCEA LAVIN</t>
+          <t>S. CAMPBELL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.3784</v>
+        <v>-2.4308</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6537</v>
+        <v>-2.5709</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2753</v>
+        <v>0.1401</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.2814</v>
+        <v>-4.4609</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.9169</v>
+        <v>-3.9403</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.3645</v>
+        <v>-0.5205</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.7746</v>
+        <v>-1.9984</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.5693</v>
+        <v>-1.6564</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2052</v>
+        <v>-0.342</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5068</v>
+        <v>-2.4625</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.3476</v>
+        <v>-2.284</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1592</v>
+        <v>-0.1785</v>
       </c>
       <c r="P20" t="n">
-        <v>0.386</v>
+        <v>-1.7371</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.158</v>
+        <v>-3.0881</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5441</v>
+        <v>1.3511</v>
       </c>
       <c r="S20" t="n">
-        <v>0.7449</v>
+        <v>2.2533</v>
       </c>
       <c r="T20" t="n">
-        <v>0.279</v>
+        <v>1.0018</v>
       </c>
       <c r="U20" t="n">
-        <v>0.466</v>
+        <v>1.2515</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.228</v>
+        <v>1.5138</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.5138</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.2668</v>
+        <v>-5.3005</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.8722</v>
+        <v>-1.7721</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.3946</v>
+        <v>-3.5284</v>
       </c>
       <c r="G21" t="n">
         <v>-2.5141</v>
@@ -2092,13 +2092,13 @@
         <v>0.772</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0892</v>
+        <v>0.0555</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1494</v>
+        <v>-0.0492</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2386</v>
+        <v>0.1048</v>
       </c>
       <c r="V21" t="n">
         <v>-2.4559</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>5.648299999999999</v>
+        <v>5.648300000000002</v>
       </c>
       <c r="E22" t="n">
-        <v>3.1513</v>
+        <v>3.151099999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>2.4972</v>
+        <v>2.4971</v>
       </c>
       <c r="G22" t="n">
         <v>0.8628999999999989</v>
@@ -2170,13 +2170,13 @@
         <v>7.720400000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>8.315399999999999</v>
+        <v>8.315199999999999</v>
       </c>
       <c r="T22" t="n">
         <v>3.6886</v>
       </c>
       <c r="U22" t="n">
-        <v>4.6267</v>
+        <v>4.6266</v>
       </c>
       <c r="V22" t="n">
         <v>5.155499999999998</v>
